--- a/recap_accuracy.xlsx
+++ b/recap_accuracy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alexandreprats/Desktop/Polytechnique/3A/Travail/P1/CSC_51054_EP/Data challenge/InTweetionists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B0CAF757-CB9C-9B41-ABDB-F382908E9D49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B8D60CF-81F9-8641-82B8-CFBF3E7AA6B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3900" yWindow="2200" windowWidth="28040" windowHeight="17440" xr2:uid="{395459CC-3156-7D43-AC99-15217102F4B8}"/>
+    <workbookView xWindow="18980" yWindow="0" windowWidth="16860" windowHeight="22400" xr2:uid="{395459CC-3156-7D43-AC99-15217102F4B8}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -35,12 +35,80 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
+  <si>
+    <t>Model architecture</t>
+  </si>
+  <si>
+    <t>Top accuracy on Kaggle set</t>
+  </si>
+  <si>
+    <t>XGBoost</t>
+  </si>
+  <si>
+    <t>0.840</t>
+  </si>
+  <si>
+    <t>Stacking of several models</t>
+  </si>
+  <si>
+    <t>0.828</t>
+  </si>
+  <si>
+    <t>Lightweight</t>
+  </si>
+  <si>
+    <t>0.837</t>
+  </si>
+  <si>
+    <t>BGE</t>
+  </si>
+  <si>
+    <t>0.836</t>
+  </si>
+  <si>
+    <t>FFNN</t>
+  </si>
+  <si>
+    <t>0.831</t>
+  </si>
+  <si>
+    <t>LightGBM</t>
+  </si>
+  <si>
+    <t>Tweetransformer</t>
+  </si>
+  <si>
+    <t>Jina</t>
+  </si>
+  <si>
+    <t>0.835</t>
+  </si>
+  <si>
+    <t>0.842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Separate models for text and metadata </t>
+  </si>
+  <si>
+    <t>0.824</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -83,6 +151,17 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6167E75C-9D56-3245-9FE2-66AA40916819}" name="Tableau1" displayName="Tableau1" ref="A1:B10" totalsRowShown="0">
+  <autoFilter ref="A1:B10" xr:uid="{6167E75C-9D56-3245-9FE2-66AA40916819}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{1FF37BA2-34BE-784C-86B1-43DDCB385C25}" name="Model architecture"/>
+    <tableColumn id="2" xr3:uid="{8B6E8452-5093-3142-925D-4832B97B4254}" name="Top accuracy on Kaggle set"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -402,9 +481,98 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E695BDA7-383E-AA43-9F61-6FD3E2338B33}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="33.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>